--- a/tests/fixtures/epar4_edd_fixture.xlsx
+++ b/tests/fixtures/epar4_edd_fixture.xlsx
@@ -759,7 +759,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Reanalysis</t>
+          <t>initial</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Reanalysis</t>
+          <t>initial</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
